--- a/doc/오류 케이스.xlsx
+++ b/doc/오류 케이스.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>입력 파일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,18 +86,6 @@
   </si>
   <si>
     <t>홈페이지 주소가 공백인 경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이런 경우에는 메세지 카드를 어떻게 보여주지?</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도 뱃지랑 행 색은 통일하는 게 좋겠음</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>위계가 있으니 일단 에러가 뜬 이상 에러를 젤 최상단으로.../</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -216,82 +204,6 @@
         <a:xfrm>
           <a:off x="5191125" y="1466850"/>
           <a:ext cx="6542857" cy="4495238"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>494552</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>142359</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6610350" y="6496050"/>
-          <a:ext cx="5980952" cy="4123809"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>332562</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>28257</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6610350" y="11106150"/>
-          <a:ext cx="6504762" cy="2542857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -566,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.125" customWidth="1"/>
@@ -656,47 +568,32 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E52" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E67" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E68" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
